--- a/Result/profitability/4562.xlsx
+++ b/Result/profitability/4562.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM46"/>
+  <dimension ref="A1:AM47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-13.60%</t>
+          <t>-13.61%</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-9.82%</t>
+          <t>-9.81%</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -6270,6 +6270,133 @@
       </c>
       <c r="AM46" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4562</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>149</v>
+      </c>
+      <c r="D47" t="n">
+        <v>80</v>
+      </c>
+      <c r="E47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F47" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-7.61%</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-0.19125</v>
+      </c>
+      <c r="N47" t="n">
+        <v>38.0125</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="X47" t="n">
+        <v>-2.272727272727273</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>5.789999999999999</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.142295404276235</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>-0.7846153846153846</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.3702830188679245</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK47" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
